--- a/doc/T294-planif-NeoJonathan.xlsx
+++ b/doc/T294-planif-NeoJonathan.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pe40boh\Documents\Github\P_Web_294-Passion_lecture-Vue.js\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pe40boh\Documents\Github\P_Web_294-Passion_lecture-Vue.js\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22C8F058-8A05-4F08-BA89-424EFCFB948E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C184676D-546B-4548-8ED2-08EF19201EE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="planif" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -699,6 +699,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-5540-4EB7-8B71-B40FAE6ADC89}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -714,6 +719,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-5540-4EB7-8B71-B40FAE6ADC89}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -729,6 +739,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-5540-4EB7-8B71-B40FAE6ADC89}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -744,6 +759,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-5540-4EB7-8B71-B40FAE6ADC89}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -759,6 +779,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-5540-4EB7-8B71-B40FAE6ADC89}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -774,6 +799,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-5540-4EB7-8B71-B40FAE6ADC89}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
@@ -791,6 +821,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-5540-4EB7-8B71-B40FAE6ADC89}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
@@ -808,10 +843,15 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-5540-4EB7-8B71-B40FAE6ADC89}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$14:$A$21</c:f>
+              <c:f>planif!$A$14:$A$21</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -843,7 +883,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$14:$B$21</c:f>
+              <c:f>planif!$B$14:$B$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>

--- a/doc/T294-planif-NeoJonathan.xlsx
+++ b/doc/T294-planif-NeoJonathan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pe40boh\Documents\Github\P_Web_294-Passion_lecture-Vue.js\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C184676D-546B-4548-8ED2-08EF19201EE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB065F11-1B26-4A7D-92E0-9DEDF951711A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -690,7 +690,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="accent4"/>
               </a:solidFill>
               <a:ln w="19050">
                 <a:solidFill>
@@ -730,7 +730,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent3"/>
+                <a:srgbClr val="FF0000"/>
               </a:solidFill>
               <a:ln w="19050">
                 <a:solidFill>
@@ -750,7 +750,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:ln w="19050">
                 <a:solidFill>
@@ -770,7 +770,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent5"/>
+                <a:srgbClr val="002060"/>
               </a:solidFill>
               <a:ln w="19050">
                 <a:solidFill>
@@ -790,7 +790,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent6"/>
+                <a:srgbClr val="0070C0"/>
               </a:solidFill>
               <a:ln w="19050">
                 <a:solidFill>
@@ -810,9 +810,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
+                <a:srgbClr val="00B0F0"/>
               </a:solidFill>
               <a:ln w="19050">
                 <a:solidFill>
@@ -832,9 +830,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
+                <a:srgbClr val="92D050"/>
               </a:solidFill>
               <a:ln w="19050">
                 <a:solidFill>

--- a/doc/T294-planif-NeoJonathan.xlsx
+++ b/doc/T294-planif-NeoJonathan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pe40boh\Documents\Github\P_Web_294-Passion_lecture-Vue.js\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB065F11-1B26-4A7D-92E0-9DEDF951711A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86250B43-977D-4520-9C91-2B4281E64DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -893,16 +893,16 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>25</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>10</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8</c:v>
@@ -2009,11 +2009,11 @@
         <v>15</v>
       </c>
       <c r="B17" s="26">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C17" s="20" t="str">
         <f t="shared" si="0"/>
-        <v>7.94%</v>
+        <v>3.17%</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="21" x14ac:dyDescent="0.35">
@@ -2021,11 +2021,11 @@
         <v>17</v>
       </c>
       <c r="B18" s="26">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C18" s="18" t="str">
         <f t="shared" si="0"/>
-        <v>39.68%</v>
+        <v>63.49%</v>
       </c>
       <c r="D18" s="24"/>
     </row>
@@ -2034,11 +2034,11 @@
         <v>18</v>
       </c>
       <c r="B19" s="25">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C19" s="18" t="str">
         <f t="shared" si="0"/>
-        <v>12.7%</v>
+        <v>3.17%</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="21" x14ac:dyDescent="0.35">
@@ -2046,11 +2046,11 @@
         <v>19</v>
       </c>
       <c r="B20" s="26">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C20" s="20" t="str">
         <f t="shared" si="0"/>
-        <v>15.87%</v>
+        <v>6.35%</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="21" x14ac:dyDescent="0.35">
